--- a/testdata/BidDetailsDataNCCF.xlsx.xlsx
+++ b/testdata/BidDetailsDataNCCF.xlsx.xlsx
@@ -456,7 +456,8 @@
     <col min="5" max="5" width="13.42578125" style="3" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" style="3" customWidth="1"/>
     <col min="7" max="8" width="12" style="3" customWidth="1"/>
-    <col min="9" max="11" width="10.28515625" style="3" customWidth="1"/>
+    <col min="9" max="10" width="10.28515625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" style="3" customWidth="1"/>
     <col min="12" max="12" width="10.85546875" style="3" customWidth="1"/>
     <col min="13" max="13" width="11.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9.140625" style="3"/>
@@ -533,27 +534,27 @@
         <v>13077124.34</v>
       </c>
       <c r="F2" s="3">
-        <v>123</v>
+        <v>1013</v>
       </c>
       <c r="G2" s="3">
         <v>100</v>
       </c>
       <c r="H2" s="3">
-        <v>60424.800000000003</v>
+        <v>51845.34</v>
       </c>
       <c r="I2" s="3">
-        <v>1827950336.5799999</v>
+        <v>1827958916.04</v>
       </c>
       <c r="J2" s="3">
-        <v>13137549.140000001</v>
+        <v>13128969.68</v>
       </c>
       <c r="L2" s="3">
         <f>D2-I2</f>
-        <v>60424.800000190735</v>
+        <v>51845.340000152588</v>
       </c>
       <c r="M2" s="3">
         <f>J2-E2</f>
-        <v>60424.800000000745</v>
+        <v>51845.339999999851</v>
       </c>
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
@@ -596,27 +597,27 @@
         <v>10011197.880000001</v>
       </c>
       <c r="F3" s="3">
-        <v>124</v>
+        <v>1014</v>
       </c>
       <c r="G3" s="3">
         <v>100</v>
       </c>
       <c r="H3" s="3">
-        <v>60928.34</v>
+        <v>51896.52</v>
       </c>
       <c r="I3" s="3">
-        <v>168405111.72</v>
+        <v>168414143.5</v>
       </c>
       <c r="J3" s="3">
-        <v>10072126.18</v>
+        <v>10063094.4</v>
       </c>
       <c r="L3" s="3">
         <f>D3-I3</f>
-        <v>60928.300000011921</v>
+        <v>51896.520000010729</v>
       </c>
       <c r="M3" s="3">
         <f>J3-E3</f>
-        <v>60928.299999998882</v>
+        <v>51896.519999999553</v>
       </c>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.25">
@@ -630,33 +631,33 @@
         <v>13</v>
       </c>
       <c r="D4" s="3">
-        <v>1033065086.78</v>
+        <v>1032942223.02</v>
       </c>
       <c r="E4" s="3">
-        <v>9093507.2799999993</v>
+        <v>9209321.4800000004</v>
       </c>
       <c r="F4" s="3">
-        <v>125</v>
+        <v>1015</v>
       </c>
       <c r="G4" s="3">
         <v>100</v>
       </c>
       <c r="H4" s="3">
-        <v>61431.88</v>
+        <v>51947.7</v>
       </c>
       <c r="I4" s="3">
-        <v>1033003654.88</v>
+        <v>1032890275.3200001</v>
       </c>
       <c r="J4" s="3">
-        <v>9154939.1799999997</v>
+        <v>9261269.1799999997</v>
       </c>
       <c r="L4" s="3">
         <f>D4-I4</f>
-        <v>61431.899999976158</v>
+        <v>51947.699999928474</v>
       </c>
       <c r="M4" s="3">
         <f>J4-E4</f>
-        <v>61431.900000000373</v>
+        <v>51947.699999999255</v>
       </c>
     </row>
   </sheetData>
